--- a/KatalonData/RADTestData/FEINandFEINSSNlessThan9Error.xlsx
+++ b/KatalonData/RADTestData/FEINandFEINSSNlessThan9Error.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{6E44AD9A-353F-4DCD-94CB-1FDE7D627846}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{E9FD8E5C-502F-4E53-9D98-9DE01386EABF}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView windowHeight="15675" windowWidth="28995" xWindow="14303" xr2:uid="{597CD883-3A55-4BEE-94D3-336F4104083C}" yWindow="-2010"/>
+    <workbookView windowHeight="16776" windowWidth="30936" xWindow="45972" xr2:uid="{597CD883-3A55-4BEE-94D3-336F4104083C}" yWindow="2952"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="138">
   <si>
     <t>Result</t>
   </si>
@@ -146,310 +146,310 @@
     <t>DoNotRun</t>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:43:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:44:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:46:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:46:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:47:30 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:48:40 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:49:50 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:51:01 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:51:07 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:51:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:51:30 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:51:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:51:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:51:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:53:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:54:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:56:10 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:57:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:57:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:57:47 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:57:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:59:02 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:00:13 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:01:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:01:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:02:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:02:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:02:50 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:02:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:03:02 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:03:08 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:03:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:03:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:03:25 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:03:30 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:03:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:03:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:03:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:04:28 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:05:40 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:06:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:08:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:18:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:19:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:20:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:21:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:22:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:22:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:23:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:23:16 EST 2025</t>
+    <t>Thu May 14 16:27:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:28:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:28:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:28:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:28:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:28:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:28:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:29:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:29:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:29:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:29:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:29:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:29:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:29:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:30:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:30:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:30:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:30:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:30:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:30:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:30:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:31:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:31:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:31:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:31:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:31:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:31:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:32:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:32:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:32:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:32:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:32:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:32:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:32:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:32:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:33:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:33:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:33:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:33:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:33:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:33:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:33:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:33:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:34:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:34:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:34:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:34:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:34:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:34:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:34:55 EDT 2026</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Fri Nov 07 11:24:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:24:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:24:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:24:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:24:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:25:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:25:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:25:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:25:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:25:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:25:32 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:25:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:25:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:25:51 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:25:57 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:26:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:26:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:26:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:26:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:26:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:26:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:26:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:26:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:26:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:26:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:27:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:27:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:27:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:27:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:27:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:27:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:27:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:27:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:27:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:28:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:28:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:28:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:28:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:28:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:28:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:28:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:28:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:28:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:29:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:29:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:29:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:29:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:29:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:29:32 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 11:29:38 EST 2025</t>
+    <t>Thu May 21 22:49:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:49:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:49:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:50:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:50:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:50:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:50:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:50:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:50:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:51:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:51:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:51:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:51:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:51:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:51:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:52:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:52:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:52:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:52:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:52:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:52:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:52:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:53:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:53:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:53:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:53:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:53:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:53:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:53:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:54:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:54:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:54:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:54:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:54:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:54:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:54:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:55:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:55:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:55:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:55:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:55:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:55:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:56:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:56:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:56:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:56:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:56:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:56:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:56:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:57:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:57:13 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -820,19 +820,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5982E357-C335-4E2D-AD06-E7759BEC14C0}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G54"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.54296875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="17.54296875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="49.1796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="40.81640625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="17.7265625" collapsed="true"/>
-    <col min="7" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="17.53125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="49.19921875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="40.796875" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="17.73046875" collapsed="true"/>
+    <col min="7" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -852,12 +852,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -869,12 +869,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -886,12 +886,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -903,12 +903,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -923,12 +923,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
@@ -943,12 +943,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
@@ -960,12 +960,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -977,12 +977,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>4</v>
@@ -994,12 +994,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -1011,12 +1011,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -1031,12 +1031,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -1051,12 +1051,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>4</v>
@@ -1068,12 +1068,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -1085,12 +1085,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>4</v>
@@ -1105,12 +1105,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -1125,12 +1125,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
@@ -1145,12 +1145,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
@@ -1165,12 +1165,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -1182,12 +1182,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
@@ -1199,12 +1199,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
@@ -1219,12 +1219,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1239,12 +1239,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -1259,12 +1259,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -1279,12 +1279,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -1296,12 +1296,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -1316,12 +1316,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -1336,12 +1336,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>21</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -1356,12 +1356,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
@@ -1376,12 +1376,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
@@ -1393,12 +1393,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>21</v>
       </c>
       <c r="B31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -1410,12 +1410,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
@@ -1427,12 +1427,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
@@ -1447,12 +1447,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
@@ -1464,12 +1464,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
@@ -1484,7 +1484,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -1504,12 +1504,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
@@ -1521,12 +1521,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
@@ -1538,12 +1538,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
@@ -1555,12 +1555,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
@@ -1572,12 +1572,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>4</v>
@@ -1589,12 +1589,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
@@ -1606,12 +1606,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -1623,12 +1623,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>21</v>
       </c>
       <c r="B44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -1640,12 +1640,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>21</v>
       </c>
       <c r="B45" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -1660,12 +1660,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
@@ -1677,12 +1677,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -1697,12 +1697,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>21</v>
       </c>
       <c r="B48" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -1714,12 +1714,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
@@ -1731,12 +1731,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>21</v>
       </c>
       <c r="B50" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
@@ -1748,12 +1748,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>21</v>
       </c>
       <c r="B51" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>4</v>
@@ -1768,7 +1768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>21</v>
       </c>
@@ -1788,12 +1788,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>21</v>
       </c>
       <c r="B53" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -1806,6 +1806,23 @@
       </c>
       <c r="F53" s="1" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>21</v>
+      </c>
+      <c r="B54" t="s">
+        <v>137</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/KatalonData/RADTestData/FEINandFEINSSNlessThan9Error.xlsx
+++ b/KatalonData/RADTestData/FEINandFEINSSNlessThan9Error.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{E9FD8E5C-502F-4E53-9D98-9DE01386EABF}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F30F006-021C-4875-B5C1-D2746812023F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="16776" windowWidth="30936" xWindow="45972" xr2:uid="{597CD883-3A55-4BEE-94D3-336F4104083C}" yWindow="2952"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{597CD883-3A55-4BEE-94D3-336F4104083C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="135">
   <si>
     <t>Result</t>
   </si>
@@ -137,319 +137,310 @@
     <t>PTE Composite</t>
   </si>
   <si>
-    <t>Mon Feb 24 22:34:06 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:38:03 EST 2025</t>
-  </si>
-  <si>
     <t>DoNotRun</t>
   </si>
   <si>
-    <t>Thu May 14 16:27:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:28:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:28:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:28:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:28:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:28:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:28:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:29:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:29:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:29:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:29:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:29:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:29:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:29:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:30:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:30:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:30:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:30:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:30:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:30:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:30:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:31:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:31:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:31:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:31:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:31:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:31:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:32:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:32:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:32:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:32:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:32:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:32:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:32:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:32:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:33:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:33:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:33:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:33:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:33:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:33:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:33:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:33:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:34:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:34:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:34:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:34:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:34:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:34:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:34:55 EDT 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Thu May 21 22:49:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:49:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:49:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:50:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:50:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:50:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:50:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:50:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:50:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:51:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:51:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:51:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:51:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:51:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:51:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:52:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:52:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:52:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:52:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:52:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:52:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:52:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:53:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:53:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:53:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:53:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:53:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:53:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:53:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:54:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:54:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:54:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:54:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:54:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:54:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:54:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:55:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:55:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:55:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:55:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:55:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:55:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:56:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:56:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:56:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:56:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:56:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:56:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:56:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:57:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:57:13 EDT 2026</t>
+    <t>Wed Jun 24 23:42:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:42:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:43:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:43:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:43:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:43:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:43:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:43:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:43:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:44:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:44:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:44:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:44:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:44:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:44:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:44:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:45:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:45:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:45:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:45:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:45:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:45:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:46:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:46:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:46:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:46:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:46:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:46:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:46:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:47:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:47:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:47:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:47:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:47:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:47:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:47:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:48:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:48:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:48:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:48:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:48:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:49:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:49:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:49:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:49:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:49:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:49:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:50:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Motor Fuel Floor Tax</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 20:38:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 20:38:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:41:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:41:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:41:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:41:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:41:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:41:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:41:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:41:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:42:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:42:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:42:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:42:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:42:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:42:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:42:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:43:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:43:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:43:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:43:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:43:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:43:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:43:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:44:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:44:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:44:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:44:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:44:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:44:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:44:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:45:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:45:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:45:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:45:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:45:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:45:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:45:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:46:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:46:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:46:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:46:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:46:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:46:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:46:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:47:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:47:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:47:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:47:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:47:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:47:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:47:49 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -499,19 +490,19 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -528,10 +519,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -566,7 +557,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -618,7 +609,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -729,21 +720,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -760,7 +751,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -812,15 +803,15 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5982E357-C335-4E2D-AD06-E7759BEC14C0}">
-  <dimension ref="A1:G54"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5982E357-C335-4E2D-AD06-E7759BEC14C0}">
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
@@ -853,11 +844,11 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>87</v>
+      <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -870,11 +861,11 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>88</v>
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -887,11 +878,11 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>89</v>
+      <c r="A4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -904,11 +895,11 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>90</v>
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -924,11 +915,11 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>91</v>
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
@@ -944,11 +935,11 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>92</v>
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
@@ -961,11 +952,11 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" t="s">
-        <v>93</v>
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -978,11 +969,11 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>94</v>
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>4</v>
@@ -995,11 +986,11 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>95</v>
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -1012,11 +1003,11 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>96</v>
+      <c r="A11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -1032,11 +1023,11 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
-        <v>97</v>
+      <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -1052,11 +1043,11 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="s">
-        <v>98</v>
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>4</v>
@@ -1069,11 +1060,11 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>99</v>
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -1086,11 +1077,11 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>100</v>
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>4</v>
@@ -1106,11 +1097,11 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" t="s">
-        <v>101</v>
+      <c r="A16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -1126,11 +1117,11 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" t="s">
-        <v>102</v>
+      <c r="A17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
@@ -1146,11 +1137,11 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>103</v>
+      <c r="A18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
@@ -1166,11 +1157,11 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" t="s">
-        <v>104</v>
+      <c r="A19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -1183,11 +1174,11 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
-        <v>105</v>
+      <c r="A20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
@@ -1200,11 +1191,11 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>106</v>
+      <c r="A21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
@@ -1220,11 +1211,11 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>107</v>
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1240,11 +1231,11 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
-        <v>108</v>
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -1260,11 +1251,11 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" t="s">
-        <v>109</v>
+      <c r="A24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -1280,11 +1271,11 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" t="s">
-        <v>110</v>
+      <c r="A25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -1297,11 +1288,11 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" t="s">
-        <v>111</v>
+      <c r="A26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -1317,11 +1308,11 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" t="s">
-        <v>112</v>
+      <c r="A27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -1337,11 +1328,11 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>21</v>
-      </c>
-      <c r="B28" t="s">
-        <v>113</v>
+      <c r="A28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -1357,11 +1348,11 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B29" t="s">
-        <v>114</v>
+      <c r="A29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
@@ -1377,11 +1368,11 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" t="s">
-        <v>115</v>
+      <c r="A30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
@@ -1394,11 +1385,11 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B31" t="s">
-        <v>116</v>
+      <c r="A31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -1411,11 +1402,11 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>21</v>
-      </c>
-      <c r="B32" t="s">
-        <v>117</v>
+      <c r="A32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
@@ -1428,11 +1419,11 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>21</v>
-      </c>
-      <c r="B33" t="s">
-        <v>118</v>
+      <c r="A33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
@@ -1448,11 +1439,11 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>21</v>
-      </c>
-      <c r="B34" t="s">
-        <v>119</v>
+      <c r="A34" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
@@ -1465,11 +1456,11 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>21</v>
-      </c>
-      <c r="B35" t="s">
-        <v>120</v>
+      <c r="A35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
@@ -1485,14 +1476,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>21</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="C36" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>30</v>
@@ -1505,11 +1490,11 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>21</v>
-      </c>
-      <c r="B37" t="s">
-        <v>121</v>
+      <c r="A37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
@@ -1522,11 +1507,11 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>21</v>
-      </c>
-      <c r="B38" t="s">
-        <v>122</v>
+      <c r="A38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
@@ -1539,11 +1524,11 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" t="s">
-        <v>123</v>
+      <c r="A39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
@@ -1556,11 +1541,11 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>21</v>
-      </c>
-      <c r="B40" t="s">
-        <v>124</v>
+      <c r="A40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
@@ -1573,11 +1558,11 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>21</v>
-      </c>
-      <c r="B41" t="s">
-        <v>125</v>
+      <c r="A41" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>4</v>
@@ -1590,11 +1575,11 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>21</v>
-      </c>
-      <c r="B42" t="s">
-        <v>126</v>
+      <c r="A42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
@@ -1607,11 +1592,11 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>21</v>
-      </c>
-      <c r="B43" t="s">
-        <v>127</v>
+      <c r="A43" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -1624,11 +1609,11 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>21</v>
-      </c>
-      <c r="B44" t="s">
-        <v>128</v>
+      <c r="A44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -1641,11 +1626,11 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>21</v>
-      </c>
-      <c r="B45" t="s">
-        <v>129</v>
+      <c r="A45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -1661,11 +1646,11 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>21</v>
-      </c>
-      <c r="B46" t="s">
-        <v>130</v>
+      <c r="A46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
@@ -1678,11 +1663,11 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>21</v>
-      </c>
-      <c r="B47" t="s">
-        <v>131</v>
+      <c r="A47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -1698,11 +1683,11 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>21</v>
-      </c>
-      <c r="B48" t="s">
-        <v>132</v>
+      <c r="A48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -1715,11 +1700,11 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>21</v>
-      </c>
-      <c r="B49" t="s">
-        <v>133</v>
+      <c r="A49" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
@@ -1732,11 +1717,11 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>21</v>
-      </c>
-      <c r="B50" t="s">
-        <v>134</v>
+      <c r="A50" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
@@ -1749,14 +1734,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
-        <v>21</v>
-      </c>
-      <c r="B51" t="s">
-        <v>135</v>
-      </c>
       <c r="C51" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>30</v>
@@ -1769,14 +1748,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
-        <v>21</v>
-      </c>
-      <c r="B52" t="s">
-        <v>34</v>
-      </c>
       <c r="C52" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>7</v>
@@ -1789,14 +1762,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
-        <v>21</v>
-      </c>
-      <c r="B53" t="s">
-        <v>136</v>
-      </c>
       <c r="C53" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>7</v>
@@ -1809,11 +1776,11 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
-        <v>21</v>
-      </c>
-      <c r="B54" t="s">
-        <v>137</v>
+      <c r="A54" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
@@ -1825,9 +1792,26 @@
         <v>31</v>
       </c>
     </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A55" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B55" t="s" s="1">
+        <v>134</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>

--- a/KatalonData/RADTestData/FEINandFEINSSNlessThan9Error.xlsx
+++ b/KatalonData/RADTestData/FEINandFEINSSNlessThan9Error.xlsx
@@ -3,21 +3,21 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F30F006-021C-4875-B5C1-D2746812023F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F50D5CFB-58DF-48B0-B8B5-22DCAA30B14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{597CD883-3A55-4BEE-94D3-336F4104083C}"/>
+    <workbookView xWindow="45972" yWindow="2952" windowWidth="30936" windowHeight="16776" xr2:uid="{597CD883-3A55-4BEE-94D3-336F4104083C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="86">
   <si>
     <t>Result</t>
   </si>
@@ -140,159 +140,9 @@
     <t>DoNotRun</t>
   </si>
   <si>
-    <t>Wed Jun 24 23:42:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:42:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:43:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:43:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:43:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:43:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:43:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:43:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:43:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:44:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:44:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:44:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:44:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:44:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:44:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:44:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:45:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:45:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:45:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:45:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:45:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:45:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:46:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:46:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:46:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:46:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:46:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:46:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:46:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:47:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:47:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:47:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:47:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:47:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:47:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:47:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:48:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:48:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:48:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:48:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:48:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:49:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:49:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:49:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:49:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:49:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:49:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:50:16 EDT 2026</t>
-  </si>
-  <si>
     <t>Motor Fuel Floor Tax</t>
   </si>
   <si>
-    <t>Thu Jul 09 20:38:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 20:38:30 EDT 2026</t>
-  </si>
-  <si>
     <t>Thu Jul 09 22:41:01 EDT 2026</t>
   </si>
   <si>
@@ -441,13 +291,15 @@
   </si>
   <si>
     <t>Thu Jul 09 22:47:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 19:17:09 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -814,13 +666,13 @@
   <dimension ref="A1:F55"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.53125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="17.53125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="49.19921875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="40.796875" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="17.73046875" collapsed="true"/>
-    <col min="7" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="17.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="49.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="40.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="17.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -848,7 +700,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -865,7 +717,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -882,7 +734,7 @@
         <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -899,7 +751,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -919,7 +771,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
@@ -939,7 +791,7 @@
         <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
@@ -956,7 +808,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -973,7 +825,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>4</v>
@@ -990,7 +842,7 @@
         <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -1007,7 +859,7 @@
         <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -1027,7 +879,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -1047,7 +899,7 @@
         <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>4</v>
@@ -1064,7 +916,7 @@
         <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -1081,7 +933,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>4</v>
@@ -1101,7 +953,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -1121,7 +973,7 @@
         <v>21</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
@@ -1141,7 +993,7 @@
         <v>21</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
@@ -1161,7 +1013,7 @@
         <v>21</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -1178,7 +1030,7 @@
         <v>21</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
@@ -1195,7 +1047,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
@@ -1215,7 +1067,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1235,7 +1087,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -1255,7 +1107,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -1275,7 +1127,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -1292,7 +1144,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -1312,7 +1164,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -1332,7 +1184,7 @@
         <v>21</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -1352,7 +1204,7 @@
         <v>21</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
@@ -1372,7 +1224,7 @@
         <v>21</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
@@ -1389,7 +1241,7 @@
         <v>21</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -1406,7 +1258,7 @@
         <v>21</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
@@ -1423,7 +1275,7 @@
         <v>21</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
@@ -1443,7 +1295,7 @@
         <v>21</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
@@ -1460,7 +1312,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
@@ -1494,7 +1346,7 @@
         <v>21</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
@@ -1511,7 +1363,7 @@
         <v>21</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
@@ -1528,7 +1380,7 @@
         <v>21</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
@@ -1545,7 +1397,7 @@
         <v>21</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
@@ -1562,7 +1414,7 @@
         <v>21</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>4</v>
@@ -1579,7 +1431,7 @@
         <v>21</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
@@ -1596,7 +1448,7 @@
         <v>21</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -1613,7 +1465,7 @@
         <v>21</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -1630,7 +1482,7 @@
         <v>21</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -1650,7 +1502,7 @@
         <v>21</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
@@ -1667,7 +1519,7 @@
         <v>21</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -1687,7 +1539,7 @@
         <v>21</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -1704,7 +1556,7 @@
         <v>21</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
@@ -1721,7 +1573,7 @@
         <v>21</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
@@ -1762,8 +1614,14 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B53" t="s">
+        <v>85</v>
+      </c>
       <c r="C53" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>7</v>
@@ -1780,7 +1638,7 @@
         <v>21</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
@@ -1796,8 +1654,8 @@
       <c r="A55" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B55" t="s" s="1">
-        <v>134</v>
+      <c r="B55" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
@@ -1806,7 +1664,7 @@
         <v>7</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
